--- a/JsonConverter/ExcelFiles/PlayerData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B090B-1563-4FD1-B167-BCA9A862A835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F471BADF-AED1-4387-AB09-BB90654109F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t xml:space="preserve">Player </t>
   </si>
@@ -40,9 +40,6 @@
     <t>이동 속도</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -67,7 +64,19 @@
     <t>MoveSpeed</t>
   </si>
   <si>
-    <t>player_1</t>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>player1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -75,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -94,6 +103,13 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -117,9 +133,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -338,90 +355,102 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1">
         <v>100</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>30</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>20</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>30</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>1.8</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/PlayerData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18828" windowHeight="6792"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="6792"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,60 +19,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+  <x:si>
+    <x:t>HungerDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThirstDecrease</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기 감소량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 갈증</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증 감소량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기 데미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThirstDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기 감소 간격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThirstInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">최대 허기 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Player_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackPower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
   <x:si>
     <x:t>MaxHunger</x:t>
   </x:si>
   <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
     <x:t>MaxThirst</x:t>
   </x:si>
   <x:si>
-    <x:t>AttackPower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Player_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">최대허기 </x:t>
-  </x:si>
-  <x:si>
     <x:t>player1</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Player </x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
     <x:t>name</x:t>
   </x:si>
   <x:si>
-    <x:t>최대목마름</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>이동 속도</x:t>
   </x:si>
   <x:si>
-    <x:t>최대체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Player </x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
     <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HungerDecrease</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증 데미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HungerInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증 감소 간격</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -144,10 +180,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -754,88 +790,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L4"/>
+  <x:dimension ref="A1:M4"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <x:cols>
+    <x:col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <x:col min="9" max="9" width="13.66796875" customWidth="1"/>
+    <x:col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <x:col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <x:col min="12" max="12" width="13.66796875" customWidth="1"/>
+    <x:col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="13.199999999999999">
+    <x:row r="1" spans="1:13" ht="13.199999999999999">
       <x:c r="A1" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="M1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:13" ht="13.199999999999999">
+      <x:c r="A2" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13" ht="13.199999999999999">
+      <x:c r="A3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:13" ht="13.199999999999999">
+      <x:c r="A4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12" ht="13.199999999999999">
-      <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I2" s="1"/>
-      <x:c r="J2" s="1"/>
-      <x:c r="K2" s="1"/>
-      <x:c r="L2" s="1"/>
-    </x:row>
-    <x:row r="3" spans="1:7" ht="13.199999999999999">
-      <x:c r="A3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7" ht="13.199999999999999">
-      <x:c r="A4" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>100</x:v>
@@ -852,9 +946,27 @@
       <x:c r="G4" s="1">
         <x:v>1.8</x:v>
       </x:c>
+      <x:c r="H4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L4">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M4">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PlayerData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerData.xlsx
@@ -21,10 +21,55 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <x:si>
+    <x:t>AttackPower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Player_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기 감소 간격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증 감소 간격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxThirst</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThirstDecrease</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HungerInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThirstDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HungerDecrease</x:t>
+  </x:si>
+  <x:si>
     <x:t>HungerDamage</x:t>
   </x:si>
   <x:si>
-    <x:t>ThirstDecrease</x:t>
+    <x:t>ThirstInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>허기 감소량</x:t>
@@ -33,82 +78,37 @@
     <x:t>최대 체력</x:t>
   </x:si>
   <x:si>
+    <x:t>허기 데미지</x:t>
+  </x:si>
+  <x:si>
     <x:t>최대 갈증</x:t>
   </x:si>
   <x:si>
     <x:t>갈증 감소량</x:t>
   </x:si>
   <x:si>
-    <x:t>허기 데미지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThirstDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기 감소 간격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThirstInterval</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">최대 허기 </x:t>
   </x:si>
   <x:si>
-    <x:t>Player_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackPower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxThirst</x:t>
+    <x:t xml:space="preserve">Player </x:t>
+  </x:si>
+  <x:si>
+    <x:t>name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동 속도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증 데미지</x:t>
   </x:si>
   <x:si>
     <x:t>player1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Player </x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동 속도</x:t>
-  </x:si>
-  <x:si>
     <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HungerDecrease</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증 데미지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HungerInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증 감소 간격</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -176,7 +176,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -793,180 +796,181 @@
   <x:dimension ref="A1:M4"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
-    <x:col min="8" max="8" width="13.5546875" customWidth="1"/>
-    <x:col min="9" max="9" width="13.66796875" customWidth="1"/>
-    <x:col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <x:col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <x:col min="12" max="12" width="13.66796875" customWidth="1"/>
-    <x:col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="13.5546875" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="13.66796875" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="14.33203125" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="13.33203125" style="1" customWidth="1"/>
+    <x:col min="12" max="12" width="13.66796875" style="1" customWidth="1"/>
+    <x:col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13" ht="13.199999999999999">
-      <x:c r="A1" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="A1" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="F1" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="M1" t="s">
+      <x:c r="J1" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.199999999999999">
-      <x:c r="A2" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M2" t="s">
-        <x:v>10</x:v>
+      <x:c r="A2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13" ht="13.199999999999999">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L3" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M3" s="1" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="J3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="13.199999999999999">
-      <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C4" s="1">
+      <x:c r="A4" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C4" s="2">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D4" s="1">
+      <x:c r="D4" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E4" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F4" s="2">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E4" s="1">
+      <x:c r="G4" s="2">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="H4" s="1">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F4" s="1">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G4" s="1">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="H4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I4">
+      <x:c r="I4" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J4">
+      <x:c r="J4" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K4">
+      <x:c r="K4" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L4">
+      <x:c r="L4" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M4">
+      <x:c r="M4" s="1">
         <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>